--- a/data_voor_swing/gebiedsdefinities/woningmarkt.xlsx
+++ b/data_voor_swing/gebiedsdefinities/woningmarkt.xlsx
@@ -481,12 +481,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Midden-Limburg Oost</t>
+          <t>MIDDEN-LIMBURG OOST</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Midden-Limburg Oost</t>
+          <t>MIDDEN-LIMBURG OOST</t>
         </is>
       </c>
     </row>
@@ -501,12 +501,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Midden-Limburg West</t>
+          <t>MIDDEN-LIMBURG WEST</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Midden-Limburg West</t>
+          <t>MIDDEN-LIMBURG WEST</t>
         </is>
       </c>
     </row>
@@ -521,12 +521,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Noord-Limburg</t>
+          <t>NOORD-LIMBURG</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Noord-Limburg</t>
+          <t>NOORD-LIMBURG</t>
         </is>
       </c>
     </row>
@@ -541,12 +541,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Noordoost-Limburg</t>
+          <t>NOORDOOST-LIMBURG</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Noordoost-Limburg</t>
+          <t>NOORDOOST-LIMBURG</t>
         </is>
       </c>
     </row>
@@ -561,12 +561,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Noordwest-Limburg</t>
+          <t>NOORDWEST-LIMBURG</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Noordwest-Limburg</t>
+          <t>NOORDWEST-LIMBURG</t>
         </is>
       </c>
     </row>
@@ -581,12 +581,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Oost-Limburg</t>
+          <t>OOST-LIMBURG</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Oost-Limburg</t>
+          <t>OOST-LIMBURG</t>
         </is>
       </c>
     </row>
@@ -601,12 +601,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Voeren</t>
+          <t>VOEREN</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Voeren</t>
+          <t>VOEREN</t>
         </is>
       </c>
     </row>
@@ -621,12 +621,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>West-Limburg</t>
+          <t>WEST-LIMBURG</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>West-Limburg</t>
+          <t>WEST-LIMBURG</t>
         </is>
       </c>
     </row>
@@ -641,12 +641,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Zuidoost-Limburg</t>
+          <t>ZUIDOOST-LIMBURG</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Zuidoost-Limburg</t>
+          <t>ZUIDOOST-LIMBURG</t>
         </is>
       </c>
     </row>
@@ -661,12 +661,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Zuidwest-Limburg</t>
+          <t>ZUIDWEST-LIMBURG</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Zuidwest-Limburg</t>
+          <t>ZUIDWEST-LIMBURG</t>
         </is>
       </c>
     </row>
